--- a/information_request_forms/014_social_media_verification_request_form--information_request_forms.xlsx
+++ b/information_request_forms/014_social_media_verification_request_form--information_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="41" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>social_media_platform</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Social Media Verification Request Form</t>
+          <t>Social Media Platform</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,27 +538,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>account_type</t>
+          <t>user_name</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Account Type</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Please select the type of your account.</t>
-        </is>
-      </c>
+          <t>User Name</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -570,41 +566,41 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>user_name</t>
+          <t>user_email</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>User Name</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>social_media_platform</t>
+          <t>phone_number</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Social Media Platform</t>
+          <t>Phone Number</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -616,18 +612,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>user_email</t>
+          <t>user_address</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>User Email</t>
+          <t>User Address</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -639,18 +635,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>phone_number</t>
+          <t>upload_proof</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Phone Number</t>
+          <t>Proof</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -662,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>user_address</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>User Address</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -680,23 +676,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>file_proof</t>
+          <t>submit_button</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Proof</t>
+          <t>Submit</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -708,386 +704,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>upload_evidence</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Evidence</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>submit_button</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Submit</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>upload_proof</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Proof</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>verify</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Verify</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>upload_evidence</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Evidence</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>uploaded_proof</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Proof</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>uploaded_evidence_2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>More</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>submitted</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Submitted</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>submitted_2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Submitted</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>uploaded_evidence_3</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>More</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>submitted_3</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Submitted</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>uploaded_evidence_4</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>More</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>submitted_4</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Submitted</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>uploaded_evidence_5</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>More</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>submitted_5</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Submitted</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>uploaded_evidence_6</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>More</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>submitted_5</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Submitted</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1102,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -1130,34 +758,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>account_type_choices</t>
+          <t>social_media_platform_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Facebook</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>account_type_choices</t>
+          <t>social_media_platform_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>twitter</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Twitter</t>
         </is>
       </c>
     </row>
@@ -1169,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Instagram</t>
         </is>
       </c>
     </row>
@@ -1186,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>twitter</t>
+          <t>tiktok</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Twitter</t>
+          <t>TikTok</t>
         </is>
       </c>
     </row>
@@ -1203,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>instagram</t>
+          <t>twitch</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Twitch</t>
         </is>
       </c>
     </row>
@@ -1220,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>tiktok</t>
+          <t>youtube</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>YouTube</t>
         </is>
       </c>
     </row>
@@ -1237,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>twitch</t>
+          <t>snapchat</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Twitch</t>
+          <t>Snapchat</t>
         </is>
       </c>
     </row>
@@ -1254,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>youtube</t>
+          <t>discord</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Discord</t>
         </is>
       </c>
     </row>
@@ -1271,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>snapchat</t>
+          <t>reddit</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Snapchat</t>
+          <t>Reddit</t>
         </is>
       </c>
     </row>
@@ -1288,12 +916,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>discord</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Discord</t>
+          <t>LinkedIn</t>
         </is>
       </c>
     </row>
@@ -1305,114 +933,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>reddit</t>
+          <t>steam</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Reddit</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>social_media_platform_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>pinterest</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Pinterest</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>social_media_platform_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>linkedin</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>social_media_platform_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>steam</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
           <t>Steam</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>social_media_platform_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>skype</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Skype</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>social_media_platform_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>whatsapp</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>WhatsApp</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>social_media_platform_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>vk</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>VK</t>
         </is>
       </c>
     </row>
